--- a/output/2026-09-06_04_Slovenia_Koroska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_04_Slovenia_Koroska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore/rivenditore B2B di pneumatica, idraulica, utensili e linee tecnologiche per industria metalmeccanica. Indirizzo: Koroška cesta 14, 2390 Ravne na Koroškem. Verificato su bizi.si/dnb.com.</t>
+          <t>Distributore/rivenditore B2B di pneumatica, idraulica, utensili e linee tecnologiche per industria metalmeccanica. Indirizzo: Koroška cesta 14, 2390 Ravne na Koroškem. Verificato su bizi.si/dnb.com. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore B2B di utensili professionali (Beta, Bosch, Milwaukee), utensili da taglio, idraulica, forniture per manutenzione officine. Indirizzo: Dobja vas 128, 2390 Ravne na Koroškem. Verificato su sito ufficiale.</t>
+          <t>Distributore B2B di utensili professionali (Beta, Bosch, Milwaukee), utensili da taglio, idraulica, forniture per manutenzione officine. Indirizzo: Dobja vas 128, 2390 Ravne na Koroškem. Verificato su sito ufficiale. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rivenditore di utensili elettrici/pneumatici, apparati per saldatura, utensili da taglio e molatura, accessori di misura per officine. Indirizzo: Partizanska cesta 15, 2390 Ravne na Koroškem. Verificato su bizi.si/ebonitete.si.</t>
+          <t>Rivenditore di utensili elettrici/pneumatici, apparati per saldatura, utensili da taglio e molatura, accessori di misura per officine. Indirizzo: Partizanska cesta 15, 2390 Ravne na Koroškem. Verificato su bizi.si/ebonitete.si. [DUPLICATO — vedi anche: 2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Catena di distribuzione tecnica/ferramenta con reparto vendita B2B ('Prodaja podjetjem'), utensili, macchine da officina, forniture industriali. Indirizzo: Ronkova ulica 35, 2380 Slovenj Gradec. Verificato su merkur.si/itis.siol.net.</t>
+          <t>Catena di distribuzione tecnica/ferramenta con reparto vendita B2B ('Prodaja podjetjem'), utensili, macchine da officina, forniture industriali. Indirizzo: Ronkova ulica 35, 2380 Slovenj Gradec. Verificato su merkur.si/itis.siol.net. [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
